--- a/docs/StructureDefinition-DIPSOrganization.xlsx
+++ b/docs/StructureDefinition-DIPSOrganization.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:16:58+00:00</t>
+    <t>2026-09-08T11:30:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -446,7 +446,7 @@
     <t>validPeriod</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/OrganizationValidPeriod}
+    <t xml:space="preserve">Extension {http://DIPS.no/fhir/StructureDefinition/R4/Organization-validPeriod}
 </t>
   </si>
   <si>
@@ -466,7 +466,7 @@
     <t>paymentCode</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/OrganizationPaymentCode}
+    <t xml:space="preserve">Extension {http://DIPS.no/fhir/StructureDefinition/R4/Organization-paymentCode}
 </t>
   </si>
   <si>
@@ -476,7 +476,7 @@
     <t>partOfSection</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/PartOfSection}
+    <t xml:space="preserve">Extension {http://DIPS.no/fhir/StructureDefinition/R4/Organization-partOfSection}
 </t>
   </si>
   <si>
@@ -486,7 +486,7 @@
     <t>partOfDepartment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/PartOfDepartment}
+    <t xml:space="preserve">Extension {http://DIPS.no/fhir/StructureDefinition/R4/Organization-partOfDepartment}
 </t>
   </si>
   <si>
@@ -496,7 +496,7 @@
     <t>bankAccountNumber1</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/BankAccountNumber1}
+    <t xml:space="preserve">Extension {http://DIPS.no/fhir/StructureDefinition/R4/Organization-bankAccountNumber1}
 </t>
   </si>
   <si>
@@ -506,7 +506,7 @@
     <t>bankAccountNumber2</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/BankAccountNumber2}
+    <t xml:space="preserve">Extension {http://DIPS.no/fhir/StructureDefinition/R4/Organization-bankAccountNumber2}
 </t>
   </si>
   <si>
@@ -1563,7 +1563,7 @@
     <t>organizationTypeCodeId</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/OrganizationTypeCodeId}
+    <t xml:space="preserve">Extension {http://DIPS.no/fhir/StructureDefinition/R4/OrganizationTypeCodeId}
 </t>
   </si>
   <si>
@@ -1594,7 +1594,7 @@
     <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/OrganizationTypeCodeId</t>
+    <t>http://DIPS.no/fhir/StructureDefinition/R4/OrganizationTypeCodeId</t>
   </si>
   <si>
     <t>Extension.url</t>
@@ -1716,7 +1716,7 @@
     <t>departmentTypeCodeId</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DepartmentTypeCodeId}
+    <t xml:space="preserve">Extension {http://DIPS.no/fhir/StructureDefinition/R4/DepartmentTypeCodeId}
 </t>
   </si>
   <si>
@@ -1729,7 +1729,7 @@
     <t>Organization.type:DepartmentType.coding.extension:departmentTypeCodeId.url</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/DepartmentTypeCodeId</t>
+    <t>http://DIPS.no/fhir/StructureDefinition/R4/DepartmentTypeCodeId</t>
   </si>
   <si>
     <t>Organization.type:DepartmentType.coding.extension:departmentTypeCodeId.value[x]</t>
@@ -1807,7 +1807,7 @@
     <t>locationTypeCodeId</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/LocationTypeCodeId}
+    <t xml:space="preserve">Extension {http://DIPS.no/fhir/StructureDefinition/R4/LocationTypeCodeId}
 </t>
   </si>
   <si>
@@ -1820,7 +1820,7 @@
     <t>Organization.type:LocalizationType.coding.extension:locationTypeCodeId.url</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/LocationTypeCodeId</t>
+    <t>http://DIPS.no/fhir/StructureDefinition/R4/LocationTypeCodeId</t>
   </si>
   <si>
     <t>Organization.type:LocalizationType.coding.extension:locationTypeCodeId.value[x]</t>
@@ -1898,7 +1898,7 @@
     <t>sectionProfessionCodeId</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/SectionProfessionCodeId}
+    <t xml:space="preserve">Extension {http://DIPS.no/fhir/StructureDefinition/R4/SectionProfessionCodeId}
 </t>
   </si>
   <si>
@@ -1911,7 +1911,7 @@
     <t>Organization.type:SectionProfession.coding.extension:sectionProfessionCodeId.url</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/SectionProfessionCodeId</t>
+    <t>http://DIPS.no/fhir/StructureDefinition/R4/SectionProfessionCodeId</t>
   </si>
   <si>
     <t>Organization.type:SectionProfession.coding.extension:sectionProfessionCodeId.value[x]</t>
@@ -2031,7 +2031,7 @@
     <t>wardTypeCodeId</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/WardTypeCodeId}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/WardTypeCodeId}
 </t>
   </si>
   <si>
@@ -2044,7 +2044,7 @@
     <t>Organization.type:WardType.coding.extension:wardTypeCodeId.url</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/WardTypeCodeId</t>
+    <t>http://dips.no/fhir/StructureDefinition/R4/WardTypeCodeId</t>
   </si>
   <si>
     <t>Organization.type:WardType.coding.extension:wardTypeCodeId.value[x]</t>
@@ -2399,7 +2399,7 @@
     <t>addressId</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/OrganizationAddressId}
+    <t xml:space="preserve">Extension {http://DIPS.no/fhir/StructureDefinition/R4/Organization-addressId}
 </t>
   </si>
   <si>
@@ -3361,7 +3361,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="64.484375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="72.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-DIPSOrganization.xlsx
+++ b/docs/StructureDefinition-DIPSOrganization.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:30:20+00:00</t>
+    <t>2026-09-15T05:06:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSOrganization.xlsx
+++ b/docs/StructureDefinition-DIPSOrganization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12265" uniqueCount="951">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12265" uniqueCount="954">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T05:06:55+00:00</t>
+    <t>2026-09-17T19:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2361,10 +2361,20 @@
 </t>
   </si>
   <si>
+    <t>The concept of an officially registered address</t>
+  </si>
+  <si>
+    <t>Defines the concept of an officially registered address in Norway. Usually this will be the adress registered in "Folkeregisteret" for persons or "Enhetsregisteret" for organizations.</t>
+  </si>
+  <si>
     <t>Organization.address.extension:urbanDistrict</t>
   </si>
   <si>
     <t>urbanDistrict</t>
+  </si>
+  <si>
+    <t>bydel
+urban district</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://hl7.no/fhir/StructureDefinition/no-basis-urban-district}
@@ -36540,7 +36550,7 @@
         <v>76</v>
       </c>
       <c r="G291" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H291" t="s" s="2">
         <v>75</v>
@@ -36555,10 +36565,10 @@
         <v>746</v>
       </c>
       <c r="L291" t="s" s="2">
-        <v>131</v>
+        <v>747</v>
       </c>
       <c r="M291" t="s" s="2">
-        <v>132</v>
+        <v>748</v>
       </c>
       <c r="N291" s="2"/>
       <c r="O291" s="2"/>
@@ -36638,16 +36648,16 @@
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B292" t="s" s="2">
         <v>742</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="D292" t="s" s="2">
-        <v>75</v>
+        <v>751</v>
       </c>
       <c r="E292" s="2"/>
       <c r="F292" t="s" s="2">
@@ -36666,13 +36676,13 @@
         <v>75</v>
       </c>
       <c r="K292" t="s" s="2">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="L292" t="s" s="2">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="M292" t="s" s="2">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="N292" s="2"/>
       <c r="O292" s="2"/>
@@ -36752,13 +36762,13 @@
     </row>
     <row r="293">
       <c r="A293" t="s" s="2">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="B293" t="s" s="2">
         <v>742</v>
       </c>
       <c r="C293" t="s" s="2">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="D293" t="s" s="2">
         <v>75</v>
@@ -36780,13 +36790,13 @@
         <v>75</v>
       </c>
       <c r="K293" t="s" s="2">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="L293" t="s" s="2">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="M293" t="s" s="2">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="N293" s="2"/>
       <c r="O293" s="2"/>
@@ -36866,13 +36876,13 @@
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="B294" t="s" s="2">
         <v>742</v>
       </c>
       <c r="C294" t="s" s="2">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="D294" t="s" s="2">
         <v>75</v>
@@ -36894,7 +36904,7 @@
         <v>75</v>
       </c>
       <c r="K294" t="s" s="2">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="L294" t="s" s="2">
         <v>140</v>
@@ -36980,10 +36990,10 @@
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" t="s" s="2">
@@ -37009,16 +37019,16 @@
         <v>105</v>
       </c>
       <c r="L295" t="s" s="2">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="M295" t="s" s="2">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="N295" t="s" s="2">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="O295" t="s" s="2">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="P295" t="s" s="2">
         <v>75</v>
@@ -37031,7 +37041,7 @@
         <v>75</v>
       </c>
       <c r="T295" t="s" s="2">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="U295" t="s" s="2">
         <v>75</v>
@@ -37047,7 +37057,7 @@
       </c>
       <c r="Y295" s="2"/>
       <c r="Z295" t="s" s="2">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="AA295" t="s" s="2">
         <v>75</v>
@@ -37065,7 +37075,7 @@
         <v>75</v>
       </c>
       <c r="AF295" t="s" s="2">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="AG295" t="s" s="2">
         <v>76</v>
@@ -37080,13 +37090,13 @@
         <v>97</v>
       </c>
       <c r="AK295" t="s" s="2">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="AL295" t="s" s="2">
         <v>717</v>
       </c>
       <c r="AM295" t="s" s="2">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="AN295" t="s" s="2">
         <v>75</v>
@@ -37094,10 +37104,10 @@
     </row>
     <row r="296">
       <c r="A296" t="s" s="2">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" t="s" s="2">
@@ -37123,13 +37133,13 @@
         <v>105</v>
       </c>
       <c r="L296" t="s" s="2">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="M296" t="s" s="2">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="N296" t="s" s="2">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="O296" s="2"/>
       <c r="P296" t="s" s="2">
@@ -37143,7 +37153,7 @@
         <v>75</v>
       </c>
       <c r="T296" t="s" s="2">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="U296" t="s" s="2">
         <v>75</v>
@@ -37159,7 +37169,7 @@
       </c>
       <c r="Y296" s="2"/>
       <c r="Z296" t="s" s="2">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="AA296" t="s" s="2">
         <v>75</v>
@@ -37177,7 +37187,7 @@
         <v>75</v>
       </c>
       <c r="AF296" t="s" s="2">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="AG296" t="s" s="2">
         <v>76</v>
@@ -37192,7 +37202,7 @@
         <v>97</v>
       </c>
       <c r="AK296" t="s" s="2">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="AL296" t="s" s="2">
         <v>717</v>
@@ -37206,10 +37216,10 @@
     </row>
     <row r="297">
       <c r="A297" t="s" s="2">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="C297" s="2"/>
       <c r="D297" t="s" s="2">
@@ -37235,16 +37245,16 @@
         <v>177</v>
       </c>
       <c r="L297" t="s" s="2">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="M297" t="s" s="2">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="N297" t="s" s="2">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="O297" t="s" s="2">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="P297" t="s" s="2">
         <v>75</v>
@@ -37257,7 +37267,7 @@
         <v>75</v>
       </c>
       <c r="T297" t="s" s="2">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="U297" t="s" s="2">
         <v>75</v>
@@ -37293,7 +37303,7 @@
         <v>75</v>
       </c>
       <c r="AF297" t="s" s="2">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="AG297" t="s" s="2">
         <v>76</v>
@@ -37308,10 +37318,10 @@
         <v>97</v>
       </c>
       <c r="AK297" t="s" s="2">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="AL297" t="s" s="2">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="AM297" t="s" s="2">
         <v>75</v>
@@ -37322,10 +37332,10 @@
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="C298" s="2"/>
       <c r="D298" t="s" s="2">
@@ -37351,10 +37361,10 @@
         <v>177</v>
       </c>
       <c r="L298" t="s" s="2">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="M298" t="s" s="2">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="N298" s="2"/>
       <c r="O298" s="2"/>
@@ -37369,7 +37379,7 @@
         <v>75</v>
       </c>
       <c r="T298" t="s" s="2">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="U298" t="s" s="2">
         <v>75</v>
@@ -37405,7 +37415,7 @@
         <v>75</v>
       </c>
       <c r="AF298" t="s" s="2">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="AG298" t="s" s="2">
         <v>76</v>
@@ -37420,13 +37430,13 @@
         <v>97</v>
       </c>
       <c r="AK298" t="s" s="2">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="AL298" t="s" s="2">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="AM298" t="s" s="2">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="AN298" t="s" s="2">
         <v>75</v>
@@ -37434,14 +37444,14 @@
     </row>
     <row r="299">
       <c r="A299" t="s" s="2">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="C299" s="2"/>
       <c r="D299" t="s" s="2">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="E299" s="2"/>
       <c r="F299" t="s" s="2">
@@ -37463,10 +37473,10 @@
         <v>177</v>
       </c>
       <c r="L299" t="s" s="2">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="M299" t="s" s="2">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="N299" s="2"/>
       <c r="O299" s="2"/>
@@ -37481,7 +37491,7 @@
         <v>75</v>
       </c>
       <c r="T299" t="s" s="2">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="U299" t="s" s="2">
         <v>75</v>
@@ -37517,7 +37527,7 @@
         <v>75</v>
       </c>
       <c r="AF299" t="s" s="2">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="AG299" t="s" s="2">
         <v>76</v>
@@ -37532,13 +37542,13 @@
         <v>97</v>
       </c>
       <c r="AK299" t="s" s="2">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="AL299" t="s" s="2">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="AM299" t="s" s="2">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="AN299" t="s" s="2">
         <v>75</v>
@@ -37546,14 +37556,14 @@
     </row>
     <row r="300">
       <c r="A300" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="C300" s="2"/>
       <c r="D300" t="s" s="2">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="E300" s="2"/>
       <c r="F300" t="s" s="2">
@@ -37575,13 +37585,13 @@
         <v>177</v>
       </c>
       <c r="L300" t="s" s="2">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="M300" t="s" s="2">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="N300" t="s" s="2">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="O300" s="2"/>
       <c r="P300" t="s" s="2">
@@ -37595,7 +37605,7 @@
         <v>75</v>
       </c>
       <c r="T300" t="s" s="2">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="U300" t="s" s="2">
         <v>75</v>
@@ -37631,7 +37641,7 @@
         <v>75</v>
       </c>
       <c r="AF300" t="s" s="2">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="AG300" t="s" s="2">
         <v>76</v>
@@ -37646,10 +37656,10 @@
         <v>97</v>
       </c>
       <c r="AK300" t="s" s="2">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="AL300" t="s" s="2">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="AM300" t="s" s="2">
         <v>75</v>
@@ -37660,10 +37670,10 @@
     </row>
     <row r="301">
       <c r="A301" t="s" s="2">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="C301" s="2"/>
       <c r="D301" t="s" s="2">
@@ -37689,10 +37699,10 @@
         <v>177</v>
       </c>
       <c r="L301" t="s" s="2">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="M301" t="s" s="2">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="N301" s="2"/>
       <c r="O301" s="2"/>
@@ -37772,10 +37782,10 @@
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="C302" s="2"/>
       <c r="D302" t="s" s="2">
@@ -37882,13 +37892,13 @@
     </row>
     <row r="303">
       <c r="A303" t="s" s="2">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="C303" t="s" s="2">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="D303" t="s" s="2">
         <v>75</v>
@@ -37910,13 +37920,13 @@
         <v>75</v>
       </c>
       <c r="K303" t="s" s="2">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="L303" t="s" s="2">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="M303" t="s" s="2">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="N303" s="2"/>
       <c r="O303" s="2"/>
@@ -37976,7 +37986,7 @@
         <v>77</v>
       </c>
       <c r="AI303" t="s" s="2">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="AJ303" t="s" s="2">
         <v>136</v>
@@ -37985,7 +37995,7 @@
         <v>75</v>
       </c>
       <c r="AL303" t="s" s="2">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="AM303" t="s" s="2">
         <v>75</v>
@@ -37996,10 +38006,10 @@
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C304" s="2"/>
       <c r="D304" t="s" s="2">
@@ -38025,10 +38035,10 @@
         <v>177</v>
       </c>
       <c r="L304" t="s" s="2">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="M304" t="s" s="2">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="N304" s="2"/>
       <c r="O304" s="2"/>
@@ -38052,7 +38062,7 @@
         <v>75</v>
       </c>
       <c r="W304" t="s" s="2">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="X304" t="s" s="2">
         <v>75</v>
@@ -38079,7 +38089,7 @@
         <v>75</v>
       </c>
       <c r="AF304" t="s" s="2">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="AG304" t="s" s="2">
         <v>76</v>
@@ -38108,14 +38118,14 @@
     </row>
     <row r="305">
       <c r="A305" t="s" s="2">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="C305" s="2"/>
       <c r="D305" t="s" s="2">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="E305" s="2"/>
       <c r="F305" t="s" s="2">
@@ -38137,10 +38147,10 @@
         <v>177</v>
       </c>
       <c r="L305" t="s" s="2">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="M305" t="s" s="2">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="N305" s="2"/>
       <c r="O305" s="2"/>
@@ -38191,7 +38201,7 @@
         <v>75</v>
       </c>
       <c r="AF305" t="s" s="2">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="AG305" t="s" s="2">
         <v>76</v>
@@ -38206,13 +38216,13 @@
         <v>97</v>
       </c>
       <c r="AK305" t="s" s="2">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="AL305" t="s" s="2">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="AM305" t="s" s="2">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="AN305" t="s" s="2">
         <v>75</v>
@@ -38220,14 +38230,14 @@
     </row>
     <row r="306">
       <c r="A306" t="s" s="2">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="C306" s="2"/>
       <c r="D306" t="s" s="2">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="E306" s="2"/>
       <c r="F306" t="s" s="2">
@@ -38249,10 +38259,10 @@
         <v>177</v>
       </c>
       <c r="L306" t="s" s="2">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="M306" t="s" s="2">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="N306" s="2"/>
       <c r="O306" s="2"/>
@@ -38267,7 +38277,7 @@
         <v>75</v>
       </c>
       <c r="T306" t="s" s="2">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="U306" t="s" s="2">
         <v>75</v>
@@ -38303,7 +38313,7 @@
         <v>75</v>
       </c>
       <c r="AF306" t="s" s="2">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="AG306" t="s" s="2">
         <v>76</v>
@@ -38318,13 +38328,13 @@
         <v>97</v>
       </c>
       <c r="AK306" t="s" s="2">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="AL306" t="s" s="2">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="AM306" t="s" s="2">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="AN306" t="s" s="2">
         <v>75</v>
@@ -38332,10 +38342,10 @@
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="C307" s="2"/>
       <c r="D307" t="s" s="2">
@@ -38361,13 +38371,13 @@
         <v>177</v>
       </c>
       <c r="L307" t="s" s="2">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="M307" t="s" s="2">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="N307" t="s" s="2">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="O307" s="2"/>
       <c r="P307" t="s" s="2">
@@ -38417,7 +38427,7 @@
         <v>75</v>
       </c>
       <c r="AF307" t="s" s="2">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="AG307" t="s" s="2">
         <v>76</v>
@@ -38432,13 +38442,13 @@
         <v>97</v>
       </c>
       <c r="AK307" t="s" s="2">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="AL307" t="s" s="2">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="AM307" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="AN307" t="s" s="2">
         <v>75</v>
@@ -38446,10 +38456,10 @@
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="C308" s="2"/>
       <c r="D308" t="s" s="2">
@@ -38475,14 +38485,14 @@
         <v>228</v>
       </c>
       <c r="L308" t="s" s="2">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="M308" t="s" s="2">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="N308" s="2"/>
       <c r="O308" t="s" s="2">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="P308" t="s" s="2">
         <v>75</v>
@@ -38495,7 +38505,7 @@
         <v>75</v>
       </c>
       <c r="T308" t="s" s="2">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="U308" t="s" s="2">
         <v>75</v>
@@ -38531,7 +38541,7 @@
         <v>75</v>
       </c>
       <c r="AF308" t="s" s="2">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="AG308" t="s" s="2">
         <v>76</v>
@@ -38546,7 +38556,7 @@
         <v>97</v>
       </c>
       <c r="AK308" t="s" s="2">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="AL308" t="s" s="2">
         <v>729</v>
@@ -38560,10 +38570,10 @@
     </row>
     <row r="309">
       <c r="A309" t="s" s="2">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="C309" s="2"/>
       <c r="D309" t="s" s="2">
@@ -38589,14 +38599,14 @@
         <v>258</v>
       </c>
       <c r="L309" t="s" s="2">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="M309" t="s" s="2">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="N309" s="2"/>
       <c r="O309" t="s" s="2">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="P309" t="s" s="2">
         <v>75</v>
@@ -38645,7 +38655,7 @@
         <v>75</v>
       </c>
       <c r="AF309" t="s" s="2">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="AG309" t="s" s="2">
         <v>76</v>
@@ -38663,7 +38673,7 @@
         <v>376</v>
       </c>
       <c r="AL309" t="s" s="2">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="AM309" t="s" s="2">
         <v>181</v>
@@ -38674,10 +38684,10 @@
     </row>
     <row r="310">
       <c r="A310" t="s" s="2">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="C310" s="2"/>
       <c r="D310" t="s" s="2">
@@ -38786,10 +38796,10 @@
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="C311" s="2"/>
       <c r="D311" t="s" s="2">
@@ -38900,10 +38910,10 @@
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="C312" s="2"/>
       <c r="D312" t="s" s="2">
@@ -38929,13 +38939,13 @@
         <v>177</v>
       </c>
       <c r="L312" t="s" s="2">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="M312" t="s" s="2">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="N312" t="s" s="2">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="O312" s="2"/>
       <c r="P312" t="s" s="2">
@@ -38985,7 +38995,7 @@
         <v>75</v>
       </c>
       <c r="AF312" t="s" s="2">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="AG312" t="s" s="2">
         <v>76</v>
@@ -38994,7 +39004,7 @@
         <v>85</v>
       </c>
       <c r="AI312" t="s" s="2">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="AJ312" t="s" s="2">
         <v>97</v>
@@ -39014,10 +39024,10 @@
     </row>
     <row r="313">
       <c r="A313" t="s" s="2">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C313" s="2"/>
       <c r="D313" t="s" s="2">
@@ -39043,13 +39053,13 @@
         <v>99</v>
       </c>
       <c r="L313" t="s" s="2">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="M313" t="s" s="2">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="N313" t="s" s="2">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="O313" s="2"/>
       <c r="P313" t="s" s="2">
@@ -39078,10 +39088,10 @@
         <v>203</v>
       </c>
       <c r="Y313" t="s" s="2">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="Z313" t="s" s="2">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="AA313" t="s" s="2">
         <v>75</v>
@@ -39099,7 +39109,7 @@
         <v>75</v>
       </c>
       <c r="AF313" t="s" s="2">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="AG313" t="s" s="2">
         <v>76</v>
@@ -39128,10 +39138,10 @@
     </row>
     <row r="314">
       <c r="A314" t="s" s="2">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="C314" s="2"/>
       <c r="D314" t="s" s="2">
@@ -39157,13 +39167,13 @@
         <v>166</v>
       </c>
       <c r="L314" t="s" s="2">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="M314" t="s" s="2">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="N314" t="s" s="2">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="O314" s="2"/>
       <c r="P314" t="s" s="2">
@@ -39213,7 +39223,7 @@
         <v>75</v>
       </c>
       <c r="AF314" t="s" s="2">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="AG314" t="s" s="2">
         <v>76</v>
@@ -39231,7 +39241,7 @@
         <v>75</v>
       </c>
       <c r="AL314" t="s" s="2">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="AM314" t="s" s="2">
         <v>75</v>
@@ -39242,10 +39252,10 @@
     </row>
     <row r="315">
       <c r="A315" t="s" s="2">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="C315" s="2"/>
       <c r="D315" t="s" s="2">
@@ -39354,10 +39364,10 @@
     </row>
     <row r="316">
       <c r="A316" t="s" s="2">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C316" s="2"/>
       <c r="D316" t="s" s="2">
@@ -39468,10 +39478,10 @@
     </row>
     <row r="317">
       <c r="A317" t="s" s="2">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="C317" s="2"/>
       <c r="D317" t="s" s="2">
@@ -39584,10 +39594,10 @@
     </row>
     <row r="318">
       <c r="A318" t="s" s="2">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="C318" s="2"/>
       <c r="D318" t="s" s="2">
@@ -39700,10 +39710,10 @@
     </row>
     <row r="319">
       <c r="A319" t="s" s="2">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C319" s="2"/>
       <c r="D319" t="s" s="2">
@@ -39816,10 +39826,10 @@
     </row>
     <row r="320">
       <c r="A320" t="s" s="2">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="C320" s="2"/>
       <c r="D320" t="s" s="2">
@@ -39930,10 +39940,10 @@
     </row>
     <row r="321">
       <c r="A321" t="s" s="2">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="C321" s="2"/>
       <c r="D321" t="s" s="2">
@@ -40042,10 +40052,10 @@
     </row>
     <row r="322">
       <c r="A322" t="s" s="2">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="C322" s="2"/>
       <c r="D322" t="s" s="2">
@@ -40156,10 +40166,10 @@
     </row>
     <row r="323">
       <c r="A323" t="s" s="2">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="C323" s="2"/>
       <c r="D323" t="s" s="2">
@@ -40185,13 +40195,13 @@
         <v>177</v>
       </c>
       <c r="L323" t="s" s="2">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="M323" t="s" s="2">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="N323" t="s" s="2">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="O323" s="2"/>
       <c r="P323" t="s" s="2">
@@ -40241,7 +40251,7 @@
         <v>75</v>
       </c>
       <c r="AF323" t="s" s="2">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="AG323" t="s" s="2">
         <v>76</v>
@@ -40270,10 +40280,10 @@
     </row>
     <row r="324">
       <c r="A324" t="s" s="2">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="C324" s="2"/>
       <c r="D324" t="s" s="2">
@@ -40296,19 +40306,19 @@
         <v>75</v>
       </c>
       <c r="K324" t="s" s="2">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="L324" t="s" s="2">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="M324" t="s" s="2">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="N324" t="s" s="2">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="O324" t="s" s="2">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="P324" t="s" s="2">
         <v>75</v>
@@ -40357,7 +40367,7 @@
         <v>75</v>
       </c>
       <c r="AF324" t="s" s="2">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="AG324" t="s" s="2">
         <v>76</v>
@@ -40375,7 +40385,7 @@
         <v>75</v>
       </c>
       <c r="AL324" t="s" s="2">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="AM324" t="s" s="2">
         <v>75</v>
@@ -40386,10 +40396,10 @@
     </row>
     <row r="325">
       <c r="A325" t="s" s="2">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="C325" s="2"/>
       <c r="D325" t="s" s="2">
@@ -40498,10 +40508,10 @@
     </row>
     <row r="326">
       <c r="A326" t="s" s="2">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="C326" s="2"/>
       <c r="D326" t="s" s="2">
@@ -40612,14 +40622,14 @@
     </row>
     <row r="327">
       <c r="A327" t="s" s="2">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="C327" s="2"/>
       <c r="D327" t="s" s="2">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="E327" s="2"/>
       <c r="F327" t="s" s="2">
@@ -40641,10 +40651,10 @@
         <v>130</v>
       </c>
       <c r="L327" t="s" s="2">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="M327" t="s" s="2">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="N327" t="s" s="2">
         <v>162</v>
@@ -40699,7 +40709,7 @@
         <v>75</v>
       </c>
       <c r="AF327" t="s" s="2">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="AG327" t="s" s="2">
         <v>76</v>
@@ -40728,10 +40738,10 @@
     </row>
     <row r="328">
       <c r="A328" t="s" s="2">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="C328" s="2"/>
       <c r="D328" t="s" s="2">
@@ -40757,14 +40767,14 @@
         <v>198</v>
       </c>
       <c r="L328" t="s" s="2">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="M328" t="s" s="2">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="N328" s="2"/>
       <c r="O328" t="s" s="2">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="P328" t="s" s="2">
         <v>75</v>
@@ -40792,10 +40802,10 @@
         <v>203</v>
       </c>
       <c r="Y328" t="s" s="2">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="Z328" t="s" s="2">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="AA328" t="s" s="2">
         <v>75</v>
@@ -40813,7 +40823,7 @@
         <v>75</v>
       </c>
       <c r="AF328" t="s" s="2">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="AG328" t="s" s="2">
         <v>76</v>
@@ -40831,7 +40841,7 @@
         <v>75</v>
       </c>
       <c r="AL328" t="s" s="2">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="AM328" t="s" s="2">
         <v>75</v>
@@ -40842,10 +40852,10 @@
     </row>
     <row r="329">
       <c r="A329" t="s" s="2">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="C329" s="2"/>
       <c r="D329" t="s" s="2">
@@ -40868,17 +40878,17 @@
         <v>75</v>
       </c>
       <c r="K329" t="s" s="2">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="L329" t="s" s="2">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="M329" t="s" s="2">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="N329" s="2"/>
       <c r="O329" t="s" s="2">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="P329" t="s" s="2">
         <v>75</v>
@@ -40927,7 +40937,7 @@
         <v>75</v>
       </c>
       <c r="AF329" t="s" s="2">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="AG329" t="s" s="2">
         <v>76</v>
@@ -40942,10 +40952,10 @@
         <v>97</v>
       </c>
       <c r="AK329" t="s" s="2">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="AL329" t="s" s="2">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="AM329" t="s" s="2">
         <v>75</v>
@@ -40956,10 +40966,10 @@
     </row>
     <row r="330">
       <c r="A330" t="s" s="2">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="C330" s="2"/>
       <c r="D330" t="s" s="2">
@@ -40985,14 +40995,14 @@
         <v>680</v>
       </c>
       <c r="L330" t="s" s="2">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="M330" t="s" s="2">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="N330" s="2"/>
       <c r="O330" t="s" s="2">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="P330" t="s" s="2">
         <v>75</v>
@@ -41041,7 +41051,7 @@
         <v>75</v>
       </c>
       <c r="AF330" t="s" s="2">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="AG330" t="s" s="2">
         <v>76</v>
@@ -41056,10 +41066,10 @@
         <v>97</v>
       </c>
       <c r="AK330" t="s" s="2">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="AL330" t="s" s="2">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="AM330" t="s" s="2">
         <v>75</v>
@@ -41070,10 +41080,10 @@
     </row>
     <row r="331">
       <c r="A331" t="s" s="2">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="C331" s="2"/>
       <c r="D331" t="s" s="2">
@@ -41182,10 +41192,10 @@
     </row>
     <row r="332">
       <c r="A332" t="s" s="2">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="C332" s="2"/>
       <c r="D332" t="s" s="2">
@@ -41296,10 +41306,10 @@
     </row>
     <row r="333">
       <c r="A333" t="s" s="2">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="C333" s="2"/>
       <c r="D333" t="s" s="2">
@@ -41358,10 +41368,10 @@
         <v>192</v>
       </c>
       <c r="Y333" t="s" s="2">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="Z333" t="s" s="2">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="AA333" t="s" s="2">
         <v>75</v>
@@ -41408,10 +41418,10 @@
     </row>
     <row r="334">
       <c r="A334" t="s" s="2">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="C334" s="2"/>
       <c r="D334" t="s" s="2">
@@ -41524,10 +41534,10 @@
     </row>
     <row r="335">
       <c r="A335" t="s" s="2">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="C335" s="2"/>
       <c r="D335" t="s" s="2">
@@ -41638,10 +41648,10 @@
     </row>
     <row r="336">
       <c r="A336" t="s" s="2">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="C336" s="2"/>
       <c r="D336" t="s" s="2">
@@ -41752,10 +41762,10 @@
     </row>
     <row r="337">
       <c r="A337" t="s" s="2">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="C337" s="2"/>
       <c r="D337" t="s" s="2">
@@ -41864,10 +41874,10 @@
     </row>
     <row r="338">
       <c r="A338" t="s" s="2">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="C338" s="2"/>
       <c r="D338" t="s" s="2">
@@ -41893,14 +41903,14 @@
         <v>731</v>
       </c>
       <c r="L338" t="s" s="2">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="M338" t="s" s="2">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="N338" s="2"/>
       <c r="O338" t="s" s="2">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="P338" t="s" s="2">
         <v>75</v>
@@ -41949,7 +41959,7 @@
         <v>75</v>
       </c>
       <c r="AF338" t="s" s="2">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="AG338" t="s" s="2">
         <v>76</v>
@@ -41964,10 +41974,10 @@
         <v>97</v>
       </c>
       <c r="AK338" t="s" s="2">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="AL338" t="s" s="2">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="AM338" t="s" s="2">
         <v>75</v>
@@ -41978,10 +41988,10 @@
     </row>
     <row r="339">
       <c r="A339" t="s" s="2">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="C339" s="2"/>
       <c r="D339" t="s" s="2">
@@ -42004,17 +42014,17 @@
         <v>75</v>
       </c>
       <c r="K339" t="s" s="2">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="L339" t="s" s="2">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="M339" t="s" s="2">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="N339" s="2"/>
       <c r="O339" t="s" s="2">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="P339" t="s" s="2">
         <v>75</v>
@@ -42063,7 +42073,7 @@
         <v>75</v>
       </c>
       <c r="AF339" t="s" s="2">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="AG339" t="s" s="2">
         <v>76</v>

--- a/docs/StructureDefinition-DIPSOrganization.xlsx
+++ b/docs/StructureDefinition-DIPSOrganization.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T19:39:02+00:00</t>
+    <t>2026-09-18T19:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSOrganization.xlsx
+++ b/docs/StructureDefinition-DIPSOrganization.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T19:41:15+00:00</t>
+    <t>2026-09-29T03:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSOrganization.xlsx
+++ b/docs/StructureDefinition-DIPSOrganization.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T03:57:01+00:00</t>
+    <t>2026-09-29T04:18:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
